--- a/test_self_healing/study_tracker.xlsx
+++ b/test_self_healing/study_tracker.xlsx
@@ -1189,7 +1189,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:00:26</t>
+          <t>2026-02-01 14:12:06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:00:26</t>
+          <t>2026-02-01 14:12:06</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1412,10 +1412,18 @@
           <t>SelfHealingStudy</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -1436,7 +1444,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:00:26</t>
+          <t>2026-02-01 14:12:06</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1610,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:00:26</t>
+          <t>2026-02-01 14:12:06</t>
         </is>
       </c>
     </row>

--- a/test_self_healing/study_tracker.xlsx
+++ b/test_self_healing/study_tracker.xlsx
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ses-01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:12:06</t>
+          <t>2026-02-01 14:38:21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ses-01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:12:06</t>
+          <t>2026-02-01 14:38:21</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ses-01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:12:06</t>
+          <t>2026-02-01 14:38:21</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ses-01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:12:06</t>
+          <t>2026-02-01 14:38:21</t>
         </is>
       </c>
     </row>

--- a/test_self_healing/study_tracker.xlsx
+++ b/test_self_healing/study_tracker.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anatomical_Status" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diffusion_Status" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relaxometry_Status" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Files" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Software_Versions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alert_History" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing_Details" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Files" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Software_Versions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alert_History" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,6 +543,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subject_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pipeline_Version</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -584,17 +627,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,406 +727,454 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quality_Metrics</t>
+          <t>Processing_Details</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quality control metrics</t>
+          <t>Fine-grained processing step parameters (matches PDF report)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data_Files</t>
+          <t>Quality_Metrics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Input/Output file paths</t>
+          <t>Quality control metrics</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software_Versions</t>
+          <t>Data_Files</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Software and pipeline versions</t>
+          <t>Input/Output file paths</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alert_History</t>
+          <t>Software_Versions</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>History of study alerts</t>
+          <t>Software and pipeline versions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Alert_History</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>High-level study summary</t>
+          <t>History of study alerts</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Subject_Metadata</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Subject demographics and metadata</t>
+          <t>High-level study summary</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Processing_Status</t>
+          <t>Subject_Metadata</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Overall pipeline status</t>
+          <t>Subject demographics and metadata</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anatomical_Status</t>
+          <t>Processing_Status</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anatomical processing details</t>
+          <t>Overall pipeline status</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Diffusion_Status</t>
+          <t>Anatomical_Status</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diffusion processing details</t>
+          <t>Anatomical processing details</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Relaxometry_Status</t>
+          <t>Diffusion_Status</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Relaxometry processing details</t>
+          <t>Diffusion processing details</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Quality_Metrics</t>
+          <t>Relaxometry_Status</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quality control metrics</t>
+          <t>Relaxometry processing details</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data_Files</t>
+          <t>Processing_Details</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Input/Output file paths</t>
+          <t>Fine-grained processing step parameters (matches PDF report)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software_Versions</t>
+          <t>Quality_Metrics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Software and pipeline versions</t>
+          <t>Quality control metrics</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alert_History</t>
+          <t>Data_Files</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>History of study alerts</t>
+          <t>Input/Output file paths</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Software_Versions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>High-level study summary</t>
+          <t>Software and pipeline versions</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Subject_Metadata</t>
+          <t>Alert_History</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Subject demographics and metadata</t>
+          <t>History of study alerts</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Processing_Status</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Overall pipeline status</t>
+          <t>High-level study summary</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Anatomical_Status</t>
+          <t>Subject_Metadata</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anatomical processing details</t>
+          <t>Subject demographics and metadata</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Diffusion_Status</t>
+          <t>Processing_Status</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Diffusion processing details</t>
+          <t>Overall pipeline status</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Relaxometry_Status</t>
+          <t>Anatomical_Status</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Relaxometry processing details</t>
+          <t>Anatomical processing details</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quality_Metrics</t>
+          <t>Diffusion_Status</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quality control metrics</t>
+          <t>Diffusion processing details</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data_Files</t>
+          <t>Relaxometry_Status</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Input/Output file paths</t>
+          <t>Relaxometry processing details</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software_Versions</t>
+          <t>Processing_Details</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Software and pipeline versions</t>
+          <t>Fine-grained processing step parameters (matches PDF report)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alert_History</t>
+          <t>Quality_Metrics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>History of study alerts</t>
+          <t>Quality control metrics</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Data_Files</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>High-level study summary</t>
+          <t>Input/Output file paths</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Subject_Metadata</t>
+          <t>Software_Versions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Subject demographics and metadata</t>
+          <t>Software and pipeline versions</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Processing_Status</t>
+          <t>Alert_History</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Overall pipeline status</t>
+          <t>History of study alerts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anatomical_Status</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Anatomical processing details</t>
+          <t>High-level study summary</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Diffusion_Status</t>
+          <t>Subject_Metadata</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diffusion processing details</t>
+          <t>Subject demographics and metadata</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Relaxometry_Status</t>
+          <t>Processing_Status</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Relaxometry processing details</t>
+          <t>Overall pipeline status</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Quality_Metrics</t>
+          <t>Anatomical_Status</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quality control metrics</t>
+          <t>Anatomical processing details</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data_Files</t>
+          <t>Diffusion_Status</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Input/Output file paths</t>
+          <t>Diffusion processing details</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software_Versions</t>
+          <t>Relaxometry_Status</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Software and pipeline versions</t>
+          <t>Relaxometry processing details</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Processing_Details</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fine-grained processing step parameters (matches PDF report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Quality_Metrics</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Quality control metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data_Files</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Input/Output file paths</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software_Versions</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Software and pipeline versions</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Alert_History</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>History of study alerts</t>
         </is>
@@ -1189,7 +1280,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:38:21</t>
+          <t>2026-02-01 16:06:21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1280,7 +1371,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:38:21</t>
+          <t>2026-02-01 16:06:21</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1444,7 +1535,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:38:21</t>
+          <t>2026-02-01 16:06:21</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1701,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-02-01 14:38:21</t>
+          <t>2026-02-01 16:06:21</t>
         </is>
       </c>
     </row>
@@ -1713,14 +1804,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1741,12 +1835,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Motion_FD_Mean</t>
+          <t>Modality</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>DWI_SNR</t>
+          <t>Step_Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
         </is>
       </c>
     </row>
@@ -1767,8 +1876,8 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1789,12 +1898,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>T1w_Present</t>
+          <t>Motion_FD_Mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>DWI_Present</t>
+          <t>DWI_SNR</t>
         </is>
       </c>
     </row>
@@ -1809,13 +1918,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1836,7 +1946,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Pipeline_Version</t>
+          <t>T1w_Present</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DWI_Present</t>
         </is>
       </c>
     </row>

--- a/test_self_healing/study_tracker.xlsx
+++ b/test_self_healing/study_tracker.xlsx
@@ -13,12 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anatomical_Status" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diffusion_Status" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relaxometry_Status" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing_Details" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Files" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Software_Versions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alert_History" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume_Statistics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROI_Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Files" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Software_Versions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alert_History" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,6 +544,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subject_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>T1w_Present</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DWI_Present</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -579,7 +628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -627,13 +676,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -727,454 +776,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Processing_Details</t>
+          <t>Volume_Statistics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fine-grained processing step parameters (matches PDF report)</t>
+          <t>Anatomical structure volumes (FSL FAST/FIRST/FreeSurfer)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quality_Metrics</t>
+          <t>ROI_Metrics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quality control metrics</t>
+          <t>Cross-modal ROI metrics (diffusion/relaxometry in anatomical ROIs)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data_Files</t>
+          <t>Quality_Metrics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Input/Output file paths</t>
+          <t>Quality control metrics</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software_Versions</t>
+          <t>Data_Files</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Software and pipeline versions</t>
+          <t>Input/Output file paths</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alert_History</t>
+          <t>Software_Versions</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>History of study alerts</t>
+          <t>Software and pipeline versions</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Alert_History</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
-        <is>
-          <t>High-level study summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Subject_Metadata</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Subject demographics and metadata</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Processing_Status</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Overall pipeline status</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Anatomical_Status</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Anatomical processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Diffusion_Status</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Diffusion processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Relaxometry_Status</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Relaxometry processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Processing_Details</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Fine-grained processing step parameters (matches PDF report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Quality_Metrics</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Quality control metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data_Files</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Input/Output file paths</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software_Versions</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Software and pipeline versions</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Alert_History</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>History of study alerts</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>High-level study summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Subject_Metadata</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Subject demographics and metadata</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Processing_Status</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Overall pipeline status</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Anatomical_Status</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Anatomical processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Diffusion_Status</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Diffusion processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Relaxometry_Status</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Relaxometry processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Processing_Details</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fine-grained processing step parameters (matches PDF report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Quality_Metrics</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Quality control metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data_Files</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Input/Output file paths</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software_Versions</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Software and pipeline versions</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Alert_History</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>History of study alerts</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>High-level study summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Subject_Metadata</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Subject demographics and metadata</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Processing_Status</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Overall pipeline status</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Anatomical_Status</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Anatomical processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Diffusion_Status</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Diffusion processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Relaxometry_Status</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Relaxometry processing details</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Processing_Details</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Fine-grained processing step parameters (matches PDF report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Quality_Metrics</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Quality control metrics</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data_Files</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Input/Output file paths</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Software_Versions</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Software and pipeline versions</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Alert_History</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
         <is>
           <t>History of study alerts</t>
         </is>
@@ -1280,7 +945,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-01 16:06:21</t>
+          <t>2026-02-03 13:49:19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1371,7 +1036,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-02-01 16:06:21</t>
+          <t>2026-02-03 13:49:19</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1382,7 +1047,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 M2:M1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 L2:L1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
       <formula1>"Complete,In Progress,Pending,Queued,Warning,Error,Failed,N/A,Manual Pass,Manual Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1396,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1404,15 +1069,16 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1443,45 +1109,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Reorienting</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Bias_Correction</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Brain_Masking</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Segmentation</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Segmentation_Method</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Coregistration</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Atlases</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall_Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Last_Update</t>
         </is>
@@ -1510,38 +1181,39 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>FreeSurfer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-02-01 16:06:21</t>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-02-03 13:49:19</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 M2:M1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 L2:L1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
       <formula1>"Complete,In Progress,Pending,Queued,Warning,Error,Failed,N/A,Manual Pass,Manual Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1701,13 +1373,13 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-02-01 16:06:21</t>
+          <t>2026-02-03 13:49:19</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 M2:M1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 L2:L1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
       <formula1>"Complete,In Progress,Pending,Queued,Warning,Error,Failed,N/A,Manual Pass,Manual Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1790,7 +1462,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 M2:M1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="D2:D1000 E2:E1000 F2:F1000 G2:G1000 H2:H1000 I2:I1000 J2:J1000 K2:K1000 L2:L1000 N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Status Selection" prompt="Please select from the list" type="list">
       <formula1>"Complete,In Progress,Pending,Queued,Warning,Error,Failed,N/A,Manual Pass,Manual Fail"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1804,17 +1476,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1835,27 +1506,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Modality</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Step_Name</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Volume_mm3</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
+          <t>ICV_Normalized</t>
         </is>
       </c>
     </row>
@@ -1865,6 +1531,78 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Subject_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ROI_Source</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ROI_Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Statistic</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1910,52 +1648,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Subject_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Session</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Study</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>T1w_Present</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DWI_Present</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>